--- a/data/positions/Posição Consolidada - 6445064.xlsx
+++ b/data/positions/Posição Consolidada - 6445064.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 6445064 | 04/09/2026, 14:13</x:t>
+    <x:t>Conta: 6445064 | 10/09/2026, 14:03</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>52,5%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 27.190.553,38</x:t>
+    <x:t>R$ 27.225.237,32</x:t>
   </x:si>
   <x:si>
     <x:t>3,70%|Prefixada</x:t>
@@ -109,10 +109,10 @@
     <x:t>R$ 300.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 379.278,72</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 367.386,91</x:t>
+    <x:t>R$ 379.803,27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 367.832,78</x:t>
   </x:si>
   <x:si>
     <x:t>CDB NBC BANK - AGO/2028</x:t>
@@ -130,10 +130,10 @@
     <x:t>R$ 200.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 256.274,67</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 247.833,47</x:t>
+    <x:t>R$ 256.649,43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 248.152,02</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BANCO ANDBANK (BRASIL) S/ - AGO/2027</x:t>
@@ -148,10 +148,10 @@
     <x:t>R$ 250.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 314.305,95</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 304.660,06</x:t>
+    <x:t>R$ 314.730,28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 305.020,74</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BANCO BBC - GRUPO SIMPAR - FEV/2027</x:t>
@@ -163,10 +163,10 @@
     <x:t>+12,30%</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 316.008,76</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 306.107,45</x:t>
+    <x:t>R$ 316.445,47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 306.478,65</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BANCO XP S.A. - AGO/2027</x:t>
@@ -175,10 +175,10 @@
     <x:t>+12,10%</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 314.873,04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 305.142,08</x:t>
+    <x:t>R$ 315.301,48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 305.506,26</x:t>
   </x:si>
   <x:si>
     <x:t>CDB FACTA FINANCEIRA - FEV/2027</x:t>
@@ -190,10 +190,10 @@
     <x:t>+12,85%</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 255.191,66</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 246.912,91</x:t>
+    <x:t>R$ 255.559,19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 247.225,31</x:t>
   </x:si>
   <x:si>
     <x:t>46,80%|Pós-Fixada</x:t>
@@ -208,10 +208,10 @@
     <x:t>117,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 271.251,73</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 260.563,97</x:t>
+    <x:t>R$ 271.743,88</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 260.982,30</x:t>
   </x:si>
   <x:si>
     <x:t>LCA BNDES - MAI/2027</x:t>
@@ -235,7 +235,7 @@
     <x:t>R$ 20.228.598,57</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 20.941.228,21</x:t>
+    <x:t>R$ 20.968.664,42</x:t>
   </x:si>
   <x:si>
     <x:t>LCA BNDES - JUN/2028</x:t>
@@ -259,7 +259,7 @@
     <x:t>R$ 924.308,74</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 940.432,51</x:t>
+    <x:t>R$ 941.613,57</x:t>
   </x:si>
   <x:si>
     <x:t>LCA BNDES - AGO/2028</x:t>
@@ -277,7 +277,7 @@
     <x:t>R$ 988.914,13</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.006.164,89</x:t>
+    <x:t>R$ 1.007.428,49</x:t>
   </x:si>
   <x:si>
     <x:t>99,00</x:t>
@@ -286,7 +286,7 @@
     <x:t>R$ 1.100.028,08</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.119.217,12</x:t>
+    <x:t>R$ 1.120.622,71</x:t>
   </x:si>
   <x:si>
     <x:t>1,80%|Inflação</x:t>
@@ -304,10 +304,10 @@
     <x:t>R$ 350.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 435.070,26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 422.309,72</x:t>
+    <x:t>R$ 435.213,91</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 422.431,82</x:t>
   </x:si>
   <x:si>
     <x:t>LF BMG - AGO/2027</x:t>
@@ -319,10 +319,10 @@
     <x:t>7,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 444.877,65</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 430.646,00</x:t>
+    <x:t>R$ 445.083,01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 430.820,56</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BANCO PLENO - AGO/2028</x:t>
@@ -346,7 +346,7 @@
     <x:t>46,6%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 24.164.391,53</x:t>
+    <x:t>R$ 24.192.387,21</x:t>
   </x:si>
   <x:si>
     <x:t>46,60%|Fundos de Renda Fixa Pós-Fixado</x:t>
@@ -367,79 +367,79 @@
     <x:t>BNP Paribas Match FIF RF CP RL</x:t>
   </x:si>
   <x:si>
+    <x:t>10/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 565,59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>904,71</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 0,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 511.696,29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 509.064,63</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 273,83</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.460,17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.864.318,23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.849.846,64</x:t>
+  </x:si>
+  <x:si>
+    <x:t>XP Crédito Estruturado 120 FIC de FIF Multimercado CP RL</x:t>
+  </x:si>
+  <x:si>
     <x:t>04/09/2026</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 564,69</x:t>
-  </x:si>
-  <x:si>
-    <x:t>904,71</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 0,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 510.882,31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 508.433,80</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 273,42</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.460,17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.859.992,95</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.846.494,54</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XP Crédito Estruturado 120 FIC de FIF Multimercado CP RL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3,22</x:t>
+    <x:t>R$ 3,23</x:t>
   </x:si>
   <x:si>
     <x:t>246.820,64</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 795.706,90</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 794.473,16</x:t>
+    <x:t>R$ 797.999,53</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 796.421,89</x:t>
   </x:si>
   <x:si>
     <x:t>Solis Capital Antares Advisory FIC de FIDC</x:t>
   </x:si>
   <x:si>
-    <x:t>02/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2,20</x:t>
+    <x:t>08/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2,21</x:t>
   </x:si>
   <x:si>
     <x:t>282.831,90</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 623.015,75</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 608.410,07</x:t>
+    <x:t>R$ 624.163,48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 609.385,64</x:t>
   </x:si>
   <x:si>
     <x:t>Riza Daikon Advisory FIF em Cotas de FIM</x:t>
   </x:si>
   <x:si>
-    <x:t>03/09/2026</x:t>
+    <x:t>09/09/2026</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 1,92</x:t>
@@ -448,55 +448,55 @@
     <x:t>100.756,91</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 192.949,92</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 191.944,08</x:t>
+    <x:t>R$ 193.238,09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 192.189,02</x:t>
   </x:si>
   <x:si>
     <x:t>Valora Horizon High Yield FIDC</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 4.825.214,25</x:t>
+    <x:t>R$ 4.831.109,41</x:t>
   </x:si>
   <x:si>
     <x:t>0,98</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 4.735.416,48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 4.588.079,56</x:t>
+    <x:t>R$ 4.741.201,93</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 4.592.997,18</x:t>
   </x:si>
   <x:si>
     <x:t>Brave 90 FIC FIDC</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2,18</x:t>
+    <x:t>R$ 2,19</x:t>
   </x:si>
   <x:si>
     <x:t>126.501,25</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 276.008,79</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 266.231,67</x:t>
+    <x:t>R$ 276.482,40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 266.634,24</x:t>
   </x:si>
   <x:si>
     <x:t>Jive BossaNova High Yield Advisory FIC FIDC</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 199,58</x:t>
+    <x:t>R$ 199,87</x:t>
   </x:si>
   <x:si>
     <x:t>30.298,33</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 6.046.815,13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.740.681,57</x:t>
+    <x:t>R$ 6.055.871,19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.748.379,23</x:t>
   </x:si>
   <x:si>
     <x:t>JGP Crédito Ecossistema 360 Advisory FIC de FIF Multimercado CP RL</x:t>
@@ -508,40 +508,40 @@
     <x:t>31.351,36</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 5.806.470,10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.781.928,29</x:t>
+    <x:t>R$ 5.806.629,09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.782.063,42</x:t>
   </x:si>
   <x:si>
     <x:t>Trend Cash CIC de Classes RF Simples RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 159,17</x:t>
+    <x:t>R$ 159,41</x:t>
   </x:si>
   <x:si>
     <x:t>591,70</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 94.181,38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 93.347,09</x:t>
+    <x:t>R$ 94.320,81</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 93.455,15</x:t>
   </x:si>
   <x:si>
     <x:t>M8 Credit Opportunities FIC de FI em FIDC</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2,73</x:t>
+    <x:t>R$ 2,74</x:t>
   </x:si>
   <x:si>
     <x:t>65.114,40</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 177.896,86</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 171.582,50</x:t>
+    <x:t>R$ 178.216,06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 171.853,82</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -553,16 +553,16 @@
     <x:t>1.383.301,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.045.054,96</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.034.917,60</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,93%|Fundos Imobiliários</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 482.800,00</x:t>
+    <x:t>R$ 2.048.250,11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.037.393,84</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,91%|Fundos Imobiliários</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 471.780,80</x:t>
   </x:si>
   <x:si>
     <x:t>Ativo</x:t>
@@ -601,10 +601,10 @@
     <x:t>R$ 102,50</x:t>
   </x:si>
   <x:si>
-    <x:t>-R$ 17,07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 85,00</x:t>
+    <x:t>-R$ 18,97</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 83,06</x:t>
   </x:si>
   <x:si>
     <x:t>0,01%|Proventos</x:t>
@@ -1263,10 +1263,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>51840584.9106885</x:v>
+        <x:v>51892245.3283176</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>51840584.9106885</x:v>
+        <x:v>51892245.3283176</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>0</x:v>
@@ -2223,7 +2223,7 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="B39" s="12" t="s">
-        <x:v>141</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C39" s="12" t="s">
         <x:v>162</x:v>

--- a/data/positions/Posição Consolidada - 6445064.xlsx
+++ b/data/positions/Posição Consolidada - 6445064.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 6445064 | 10/09/2026, 14:03</x:t>
+    <x:t>Conta: 6445064 | 21/09/2026, 16:44</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>52,5%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 27.225.237,32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3,70%|Prefixada</x:t>
+    <x:t>53,3%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 27.305.715,35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,80%|Prefixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -109,10 +109,10 @@
     <x:t>R$ 300.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 379.803,27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 367.832,78</x:t>
+    <x:t>R$ 381.030,03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 368.875,53</x:t>
   </x:si>
   <x:si>
     <x:t>CDB NBC BANK - AGO/2028</x:t>
@@ -130,10 +130,10 @@
     <x:t>R$ 200.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 256.649,43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 248.152,02</x:t>
+    <x:t>R$ 257.526,02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 248.897,12</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BANCO ANDBANK (BRASIL) S/ - AGO/2027</x:t>
@@ -148,10 +148,10 @@
     <x:t>R$ 250.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 314.730,28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 305.020,74</x:t>
+    <x:t>R$ 315.722,62</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 305.864,23</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BANCO BBC - GRUPO SIMPAR - FEV/2027</x:t>
@@ -163,10 +163,10 @@
     <x:t>+12,30%</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 316.445,47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 306.478,65</x:t>
+    <x:t>R$ 317.466,80</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 307.346,78</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BANCO XP S.A. - AGO/2027</x:t>
@@ -175,10 +175,10 @@
     <x:t>+12,10%</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 315.301,48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 305.506,26</x:t>
+    <x:t>R$ 316.303,46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 306.357,94</x:t>
   </x:si>
   <x:si>
     <x:t>CDB FACTA FINANCEIRA - FEV/2027</x:t>
@@ -190,13 +190,13 @@
     <x:t>+12,85%</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 255.559,19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 247.225,31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>46,80%|Pós-Fixada</x:t>
+    <x:t>R$ 256.418,81</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 247.955,99</x:t>
+  </x:si>
+  <x:si>
+    <x:t>47,60%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>CDB ORIGINAL - AGO/2027</x:t>
@@ -208,10 +208,10 @@
     <x:t>117,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 271.743,88</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 260.982,30</x:t>
+    <x:t>R$ 272.890,14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 261.956,62</x:t>
   </x:si>
   <x:si>
     <x:t>LCA BNDES - MAI/2027</x:t>
@@ -235,7 +235,7 @@
     <x:t>R$ 20.228.598,57</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 20.968.664,42</x:t>
+    <x:t>R$ 21.032.512,29</x:t>
   </x:si>
   <x:si>
     <x:t>LCA BNDES - JUN/2028</x:t>
@@ -259,7 +259,7 @@
     <x:t>R$ 924.308,74</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 941.613,57</x:t>
+    <x:t>R$ 944.361,80</x:t>
   </x:si>
   <x:si>
     <x:t>LCA BNDES - AGO/2028</x:t>
@@ -277,7 +277,7 @@
     <x:t>R$ 988.914,13</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.007.428,49</x:t>
+    <x:t>R$ 1.010.368,81</x:t>
   </x:si>
   <x:si>
     <x:t>99,00</x:t>
@@ -286,7 +286,7 @@
     <x:t>R$ 1.100.028,08</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.120.622,71</x:t>
+    <x:t>R$ 1.123.893,40</x:t>
   </x:si>
   <x:si>
     <x:t>1,80%|Inflação</x:t>
@@ -304,10 +304,10 @@
     <x:t>R$ 350.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 435.213,91</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 422.431,82</x:t>
+    <x:t>R$ 435.416,36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 422.603,91</x:t>
   </x:si>
   <x:si>
     <x:t>LF BMG - AGO/2027</x:t>
@@ -319,10 +319,10 @@
     <x:t>7,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 445.083,01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 430.820,56</x:t>
+    <x:t>R$ 445.426,59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 431.112,60</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BANCO PLENO - AGO/2028</x:t>
@@ -343,13 +343,13 @@
     <x:t>R$ 74.699,90</x:t>
   </x:si>
   <x:si>
-    <x:t>46,6%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 24.192.387,21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>46,60%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>45,8%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 23.431.003,70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45,70%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -367,10 +367,10 @@
     <x:t>BNP Paribas Match FIF RF CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>10/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 565,59</x:t>
+    <x:t>21/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 567,67</x:t>
   </x:si>
   <x:si>
     <x:t>904,71</x:t>
@@ -379,94 +379,76 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 511.696,29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 509.064,63</x:t>
+    <x:t>R$ 513.571,60</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 510.517,99</x:t>
   </x:si>
   <x:si>
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 273,83</x:t>
+    <x:t>R$ 274,82</x:t>
   </x:si>
   <x:si>
     <x:t>10.460,17</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.864.318,23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.849.846,64</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XP Crédito Estruturado 120 FIC de FIF Multimercado CP RL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3,23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>246.820,64</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 797.999,53</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 796.421,89</x:t>
+    <x:t>R$ 2.874.648,57</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.857.852,65</x:t>
   </x:si>
   <x:si>
     <x:t>Solis Capital Antares Advisory FIC de FIDC</x:t>
   </x:si>
   <x:si>
-    <x:t>08/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2,21</x:t>
+    <x:t>17/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2,22</x:t>
   </x:si>
   <x:si>
     <x:t>282.831,90</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 624.163,48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 609.385,64</x:t>
+    <x:t>R$ 626.751,68</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 611.585,61</x:t>
   </x:si>
   <x:si>
     <x:t>Riza Daikon Advisory FIF em Cotas de FIM</x:t>
   </x:si>
   <x:si>
-    <x:t>09/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1,92</x:t>
+    <x:t>18/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1,93</x:t>
   </x:si>
   <x:si>
     <x:t>100.756,91</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 193.238,09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 192.189,02</x:t>
+    <x:t>R$ 194.058,12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 192.886,05</x:t>
   </x:si>
   <x:si>
     <x:t>Valora Horizon High Yield FIDC</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 4.831.109,41</x:t>
+    <x:t>R$ 4.849.872,04</x:t>
   </x:si>
   <x:si>
     <x:t>0,98</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 4.741.201,93</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 4.592.997,18</x:t>
+    <x:t>R$ 4.759.615,38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 4.608.648,62</x:t>
   </x:si>
   <x:si>
     <x:t>Brave 90 FIC FIDC</x:t>
@@ -478,91 +460,91 @@
     <x:t>126.501,25</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 276.482,40</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 266.634,24</x:t>
+    <x:t>R$ 277.597,77</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 267.582,30</x:t>
   </x:si>
   <x:si>
     <x:t>Jive BossaNova High Yield Advisory FIC FIDC</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 199,87</x:t>
+    <x:t>R$ 200,66</x:t>
   </x:si>
   <x:si>
     <x:t>30.298,33</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 6.055.871,19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.748.379,23</x:t>
+    <x:t>R$ 6.079.587,35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.768.537,95</x:t>
   </x:si>
   <x:si>
     <x:t>JGP Crédito Ecossistema 360 Advisory FIC de FIF Multimercado CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 185,21</x:t>
+    <x:t>R$ 184,66</x:t>
   </x:si>
   <x:si>
     <x:t>31.351,36</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 5.806.629,09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.782.063,42</x:t>
+    <x:t>R$ 5.789.274,31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.767.311,86</x:t>
   </x:si>
   <x:si>
     <x:t>Trend Cash CIC de Classes RF Simples RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 159,41</x:t>
-  </x:si>
-  <x:si>
-    <x:t>591,70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 94.320,81</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 93.455,15</x:t>
+    <x:t>R$ 159,97</x:t>
+  </x:si>
+  <x:si>
+    <x:t>507,28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 81.147,31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 80.341,28</x:t>
   </x:si>
   <x:si>
     <x:t>M8 Credit Opportunities FIC de FI em FIDC</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2,74</x:t>
+    <x:t>R$ 2,75</x:t>
   </x:si>
   <x:si>
     <x:t>65.114,40</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 178.216,06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 171.853,82</x:t>
+    <x:t>R$ 178.971,77</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 172.496,18</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1,48</x:t>
+    <x:t>R$ 1,49</x:t>
   </x:si>
   <x:si>
     <x:t>1.383.301,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.048.250,11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.037.393,84</x:t>
+    <x:t>R$ 2.055.779,84</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.043.229,38</x:t>
   </x:si>
   <x:si>
     <x:t>0,91%|Fundos Imobiliários</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 471.780,80</x:t>
+    <x:t>R$ 465.760,00</x:t>
   </x:si>
   <x:si>
     <x:t>Ativo</x:t>
@@ -601,34 +583,16 @@
     <x:t>R$ 102,50</x:t>
   </x:si>
   <x:si>
-    <x:t>-R$ 18,97</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 83,06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,01%|Proventos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.840,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Indexador</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Data Provisão Pagamento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quantidade Provisionada</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Provisionado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RENDIMENTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14/09/2026</x:t>
+    <x:t>-R$ 20,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 82,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,01%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.873,72</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -656,6 +620,9 @@
   </x:si>
   <x:si>
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5873,72</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -1203,7 +1170,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K57"/>
+  <x:dimension ref="A1:K51"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="51.853482" style="0" customWidth="1"/>
@@ -1263,13 +1230,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>51892245.3283176</x:v>
+        <x:v>51208352.7681288</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>51892245.3283176</x:v>
+        <x:v>51202479.0481289</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>0</x:v>
+        <x:v>5873.72</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -2115,22 +2082,22 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="B35" s="12" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="C35" s="12" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="C35" s="12" t="s">
+      <x:c r="D35" s="12" t="s">
         <x:v>142</x:v>
-      </x:c>
-      <x:c r="D35" s="12" t="s">
-        <x:v>143</x:v>
       </x:c>
       <x:c r="E35" s="12" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="F35" s="12" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="G35" s="12" t="s">
         <x:v>144</x:v>
-      </x:c>
-      <x:c r="G35" s="12" t="s">
-        <x:v>145</x:v>
       </x:c>
       <x:c r="H35" s="3"/>
       <x:c r="I35" s="3"/>
@@ -2139,25 +2106,25 @@
     </x:row>
     <x:row r="36" spans="1:11" ht="30" customHeight="1">
       <x:c r="A36" s="12" t="s">
-        <x:v>146</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B36" s="12" t="s">
         <x:v>135</x:v>
       </x:c>
       <x:c r="C36" s="12" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D36" s="12" t="s">
         <x:v>147</x:v>
-      </x:c>
-      <x:c r="D36" s="12" t="s">
-        <x:v>148</x:v>
       </x:c>
       <x:c r="E36" s="12" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="F36" s="12" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="G36" s="12" t="s">
         <x:v>149</x:v>
-      </x:c>
-      <x:c r="G36" s="12" t="s">
-        <x:v>150</x:v>
       </x:c>
       <x:c r="H36" s="3"/>
       <x:c r="I36" s="3"/>
@@ -2166,25 +2133,25 @@
     </x:row>
     <x:row r="37" spans="1:11" ht="30" customHeight="1">
       <x:c r="A37" s="12" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="B37" s="12" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="C37" s="12" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="B37" s="12" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="C37" s="12" t="s">
+      <x:c r="D37" s="12" t="s">
         <x:v>152</x:v>
-      </x:c>
-      <x:c r="D37" s="12" t="s">
-        <x:v>153</x:v>
       </x:c>
       <x:c r="E37" s="12" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="F37" s="12" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="G37" s="12" t="s">
         <x:v>154</x:v>
-      </x:c>
-      <x:c r="G37" s="12" t="s">
-        <x:v>155</x:v>
       </x:c>
       <x:c r="H37" s="3"/>
       <x:c r="I37" s="3"/>
@@ -2193,25 +2160,25 @@
     </x:row>
     <x:row r="38" spans="1:11" ht="30" customHeight="1">
       <x:c r="A38" s="12" t="s">
-        <x:v>156</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B38" s="12" t="s">
         <x:v>135</x:v>
       </x:c>
       <x:c r="C38" s="12" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="D38" s="12" t="s">
         <x:v>157</x:v>
-      </x:c>
-      <x:c r="D38" s="12" t="s">
-        <x:v>158</x:v>
       </x:c>
       <x:c r="E38" s="12" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="F38" s="12" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="G38" s="12" t="s">
         <x:v>159</x:v>
-      </x:c>
-      <x:c r="G38" s="12" t="s">
-        <x:v>160</x:v>
       </x:c>
       <x:c r="H38" s="3"/>
       <x:c r="I38" s="3"/>
@@ -2220,25 +2187,25 @@
     </x:row>
     <x:row r="39" spans="1:11" ht="30" customHeight="1">
       <x:c r="A39" s="12" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="B39" s="12" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="C39" s="12" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="B39" s="12" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="C39" s="12" t="s">
+      <x:c r="D39" s="12" t="s">
         <x:v>162</x:v>
-      </x:c>
-      <x:c r="D39" s="12" t="s">
-        <x:v>163</x:v>
       </x:c>
       <x:c r="E39" s="12" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="F39" s="12" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G39" s="12" t="s">
         <x:v>164</x:v>
-      </x:c>
-      <x:c r="G39" s="12" t="s">
-        <x:v>165</x:v>
       </x:c>
       <x:c r="H39" s="3"/>
       <x:c r="I39" s="3"/>
@@ -2247,25 +2214,25 @@
     </x:row>
     <x:row r="40" spans="1:11" ht="30" customHeight="1">
       <x:c r="A40" s="12" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="B40" s="12" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="C40" s="12" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="B40" s="12" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="C40" s="12" t="s">
+      <x:c r="D40" s="12" t="s">
         <x:v>167</x:v>
-      </x:c>
-      <x:c r="D40" s="12" t="s">
-        <x:v>168</x:v>
       </x:c>
       <x:c r="E40" s="12" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="F40" s="12" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="G40" s="12" t="s">
         <x:v>169</x:v>
-      </x:c>
-      <x:c r="G40" s="12" t="s">
-        <x:v>170</x:v>
       </x:c>
       <x:c r="H40" s="3"/>
       <x:c r="I40" s="3"/>
@@ -2273,383 +2240,266 @@
       <x:c r="K40" s="3"/>
     </x:row>
     <x:row r="41" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A41" s="12" t="s">
+      <x:c r="A41" s="13" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="B41" s="13" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="C41" s="13" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="B41" s="12" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="C41" s="12" t="s">
+      <x:c r="D41" s="13" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="D41" s="12" t="s">
+      <x:c r="E41" s="13" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="F41" s="13" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="E41" s="12" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="F41" s="12" t="s">
+      <x:c r="G41" s="13" t="s">
         <x:v>174</x:v>
-      </x:c>
-      <x:c r="G41" s="12" t="s">
-        <x:v>175</x:v>
       </x:c>
       <x:c r="H41" s="3"/>
       <x:c r="I41" s="3"/>
       <x:c r="J41" s="3"/>
       <x:c r="K41" s="3"/>
     </x:row>
-    <x:row r="42" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A42" s="13" t="s">
+    <x:row r="42" spans="1:11">
+      <x:c r="A42" s="4"/>
+      <x:c r="B42" s="4"/>
+      <x:c r="C42" s="4"/>
+      <x:c r="D42" s="4"/>
+      <x:c r="E42" s="4"/>
+      <x:c r="F42" s="4"/>
+      <x:c r="G42" s="4"/>
+      <x:c r="H42" s="4"/>
+      <x:c r="I42" s="4"/>
+      <x:c r="J42" s="4"/>
+      <x:c r="K42" s="4"/>
+    </x:row>
+    <x:row r="43" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A43" s="8" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="B43" s="9"/>
+      <x:c r="C43" s="9"/>
+      <x:c r="D43" s="9"/>
+      <x:c r="E43" s="9"/>
+      <x:c r="F43" s="9"/>
+      <x:c r="G43" s="9"/>
+      <x:c r="H43" s="9"/>
+      <x:c r="I43" s="9"/>
+      <x:c r="J43" s="9"/>
+      <x:c r="K43" s="10" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="B42" s="13" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="C42" s="13" t="s">
+    </x:row>
+    <x:row r="44" spans="1:11">
+      <x:c r="A44" s="4"/>
+      <x:c r="B44" s="4"/>
+      <x:c r="C44" s="4"/>
+      <x:c r="D44" s="4"/>
+      <x:c r="E44" s="4"/>
+      <x:c r="F44" s="4"/>
+      <x:c r="G44" s="4"/>
+      <x:c r="H44" s="4"/>
+      <x:c r="I44" s="4"/>
+      <x:c r="J44" s="4"/>
+      <x:c r="K44" s="4"/>
+    </x:row>
+    <x:row r="45" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A45" s="11" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="D42" s="13" t="s">
+      <x:c r="B45" s="11" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="E42" s="13" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="F42" s="13" t="s">
+      <x:c r="C45" s="11" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="G42" s="13" t="s">
+      <x:c r="D45" s="11" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="H42" s="3"/>
-      <x:c r="I42" s="3"/>
-      <x:c r="J42" s="3"/>
-      <x:c r="K42" s="3"/>
-    </x:row>
-    <x:row r="43" spans="1:11">
-      <x:c r="A43" s="4"/>
-      <x:c r="B43" s="4"/>
-      <x:c r="C43" s="4"/>
-      <x:c r="D43" s="4"/>
-      <x:c r="E43" s="4"/>
-      <x:c r="F43" s="4"/>
-      <x:c r="G43" s="4"/>
-      <x:c r="H43" s="4"/>
-      <x:c r="I43" s="4"/>
-      <x:c r="J43" s="4"/>
-      <x:c r="K43" s="4"/>
-    </x:row>
-    <x:row r="44" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A44" s="8" t="s">
+      <x:c r="E45" s="11" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="B44" s="9"/>
-      <x:c r="C44" s="9"/>
-      <x:c r="D44" s="9"/>
-      <x:c r="E44" s="9"/>
-      <x:c r="F44" s="9"/>
-      <x:c r="G44" s="9"/>
-      <x:c r="H44" s="9"/>
-      <x:c r="I44" s="9"/>
-      <x:c r="J44" s="9"/>
-      <x:c r="K44" s="10" t="s">
+      <x:c r="F45" s="11" t="s">
         <x:v>182</x:v>
       </x:c>
-    </x:row>
-    <x:row r="45" spans="1:11">
-      <x:c r="A45" s="4"/>
-      <x:c r="B45" s="4"/>
-      <x:c r="C45" s="4"/>
-      <x:c r="D45" s="4"/>
-      <x:c r="E45" s="4"/>
-      <x:c r="F45" s="4"/>
-      <x:c r="G45" s="4"/>
-      <x:c r="H45" s="4"/>
-      <x:c r="I45" s="4"/>
-      <x:c r="J45" s="4"/>
-      <x:c r="K45" s="4"/>
-    </x:row>
-    <x:row r="46" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A46" s="11" t="s">
+      <x:c r="G45" s="11" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="B46" s="11" t="s">
+      <x:c r="H45" s="11" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="I45" s="11" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="C46" s="11" t="s">
+      <x:c r="J45" s="11" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="D46" s="11" t="s">
+      <x:c r="K45" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A46" s="13" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="E46" s="11" t="s">
+      <x:c r="B46" s="13" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="F46" s="11" t="s">
+      <x:c r="C46" s="13" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D46" s="13" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E46" s="13" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F46" s="13" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="G46" s="13" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="G46" s="11" t="s">
+      <x:c r="H46" s="13" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="I46" s="13" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="H46" s="11" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="I46" s="11" t="s">
+      <x:c r="J46" s="13" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="J46" s="11" t="s">
+      <x:c r="K46" s="13" t="s">
+        <x:v>176</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:11">
+      <x:c r="A47" s="4"/>
+      <x:c r="B47" s="4"/>
+      <x:c r="C47" s="4"/>
+      <x:c r="D47" s="4"/>
+      <x:c r="E47" s="4"/>
+      <x:c r="F47" s="4"/>
+      <x:c r="G47" s="4"/>
+      <x:c r="H47" s="4"/>
+      <x:c r="I47" s="4"/>
+      <x:c r="J47" s="4"/>
+      <x:c r="K47" s="4"/>
+    </x:row>
+    <x:row r="48" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A48" s="8" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="K46" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A47" s="13" t="s">
+      <x:c r="B48" s="9"/>
+      <x:c r="C48" s="9"/>
+      <x:c r="D48" s="9"/>
+      <x:c r="E48" s="9"/>
+      <x:c r="F48" s="9"/>
+      <x:c r="G48" s="9"/>
+      <x:c r="H48" s="9"/>
+      <x:c r="I48" s="9"/>
+      <x:c r="J48" s="9"/>
+      <x:c r="K48" s="10" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="B47" s="13" t="s">
+    </x:row>
+    <x:row r="49" spans="1:11">
+      <x:c r="A49" s="4"/>
+      <x:c r="B49" s="4"/>
+      <x:c r="C49" s="4"/>
+      <x:c r="D49" s="4"/>
+      <x:c r="E49" s="4"/>
+      <x:c r="F49" s="4"/>
+      <x:c r="G49" s="4"/>
+      <x:c r="H49" s="4"/>
+      <x:c r="I49" s="4"/>
+      <x:c r="J49" s="4"/>
+      <x:c r="K49" s="4"/>
+    </x:row>
+    <x:row r="50" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A50" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B50" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C50" s="11" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="C47" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D47" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E47" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F47" s="13" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="G47" s="13" t="s">
+      <x:c r="D50" s="11" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="H47" s="13" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="I47" s="13" t="s">
+      <x:c r="E50" s="11" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="J47" s="13" t="s">
+      <x:c r="F50" s="11" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="K47" s="13" t="s">
-        <x:v>182</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:11">
-      <x:c r="A48" s="4"/>
-      <x:c r="B48" s="4"/>
-      <x:c r="C48" s="4"/>
-      <x:c r="D48" s="4"/>
-      <x:c r="E48" s="4"/>
-      <x:c r="F48" s="4"/>
-      <x:c r="G48" s="4"/>
-      <x:c r="H48" s="4"/>
-      <x:c r="I48" s="4"/>
-      <x:c r="J48" s="4"/>
-      <x:c r="K48" s="4"/>
-    </x:row>
-    <x:row r="49" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A49" s="8" t="s">
+      <x:c r="G50" s="11" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="B49" s="9"/>
-      <x:c r="C49" s="9"/>
-      <x:c r="D49" s="9"/>
-      <x:c r="E49" s="9"/>
-      <x:c r="F49" s="9"/>
-      <x:c r="G49" s="10" t="s">
+      <x:c r="H50" s="11" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="H49" s="3"/>
-      <x:c r="I49" s="3"/>
-      <x:c r="J49" s="3"/>
-      <x:c r="K49" s="3"/>
-    </x:row>
-    <x:row r="50" spans="1:11">
-      <x:c r="A50" s="4"/>
-      <x:c r="B50" s="4"/>
-      <x:c r="C50" s="4"/>
-      <x:c r="D50" s="4"/>
-      <x:c r="E50" s="4"/>
-      <x:c r="F50" s="4"/>
-      <x:c r="G50" s="4"/>
-      <x:c r="H50" s="3"/>
-      <x:c r="I50" s="3"/>
-      <x:c r="J50" s="3"/>
-      <x:c r="K50" s="3"/>
-    </x:row>
-    <x:row r="51" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A51" s="11" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="B51" s="11" t="s">
+      <x:c r="I50" s="11" t="s">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="C51" s="11" t="s">
+      <x:c r="J50" s="11" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="D51" s="11" t="s">
+      <x:c r="K50" s="11" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="E51" s="11" t="s">
+    </x:row>
+    <x:row r="51" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A51" s="13" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="F51" s="3"/>
-      <x:c r="G51" s="3"/>
-      <x:c r="H51" s="3"/>
-      <x:c r="I51" s="3"/>
-      <x:c r="J51" s="3"/>
-      <x:c r="K51" s="3"/>
-    </x:row>
-    <x:row r="52" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A52" s="13" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="B52" s="13" t="s">
+      <x:c r="B51" s="13" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="C52" s="13" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="D52" s="13" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="E52" s="13" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="F52" s="3"/>
-      <x:c r="G52" s="3"/>
-      <x:c r="H52" s="3"/>
-      <x:c r="I52" s="3"/>
-      <x:c r="J52" s="3"/>
-      <x:c r="K52" s="3"/>
-    </x:row>
-    <x:row r="53" spans="1:11">
-      <x:c r="A53" s="4"/>
-      <x:c r="B53" s="4"/>
-      <x:c r="C53" s="4"/>
-      <x:c r="D53" s="4"/>
-      <x:c r="E53" s="4"/>
-      <x:c r="F53" s="4"/>
-      <x:c r="G53" s="4"/>
-      <x:c r="H53" s="4"/>
-      <x:c r="I53" s="4"/>
-      <x:c r="J53" s="4"/>
-      <x:c r="K53" s="4"/>
-    </x:row>
-    <x:row r="54" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A54" s="8" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B54" s="9"/>
-      <x:c r="C54" s="9"/>
-      <x:c r="D54" s="9"/>
-      <x:c r="E54" s="9"/>
-      <x:c r="F54" s="9"/>
-      <x:c r="G54" s="9"/>
-      <x:c r="H54" s="9"/>
-      <x:c r="I54" s="9"/>
-      <x:c r="J54" s="9"/>
-      <x:c r="K54" s="10" t="s">
-        <x:v>120</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:11">
-      <x:c r="A55" s="4"/>
-      <x:c r="B55" s="4"/>
-      <x:c r="C55" s="4"/>
-      <x:c r="D55" s="4"/>
-      <x:c r="E55" s="4"/>
-      <x:c r="F55" s="4"/>
-      <x:c r="G55" s="4"/>
-      <x:c r="H55" s="4"/>
-      <x:c r="I55" s="4"/>
-      <x:c r="J55" s="4"/>
-      <x:c r="K55" s="4"/>
-    </x:row>
-    <x:row r="56" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A56" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B56" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C56" s="11" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="D56" s="11" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="E56" s="11" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="F56" s="11" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="G56" s="11" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="H56" s="11" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="I56" s="11" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="J56" s="11" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="K56" s="11" t="s">
-        <x:v>213</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A57" s="13" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="B57" s="13" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="C57" s="13" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="D57" s="13" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="E57" s="13" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="F57" s="13" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="G57" s="13" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="H57" s="13" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="I57" s="13" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="J57" s="13" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="K57" s="13" t="s">
-        <x:v>214</x:v>
+      <x:c r="C51" s="13" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="D51" s="13" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="E51" s="13" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="F51" s="13" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G51" s="13" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="H51" s="13" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="I51" s="13" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="J51" s="13" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="K51" s="13" t="s">
+        <x:v>203</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="7">
+  <x:mergeCells count="6">
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
     <x:mergeCell ref="A28:F28"/>
-    <x:mergeCell ref="A44:J44"/>
-    <x:mergeCell ref="A49:F49"/>
-    <x:mergeCell ref="A54:J54"/>
+    <x:mergeCell ref="A43:J43"/>
+    <x:mergeCell ref="A48:J48"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 6445064.xlsx
+++ b/data/positions/Posição Consolidada - 6445064.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 6445064 | 21/09/2026, 16:44</x:t>
+    <x:t>Conta: 6445064 | 23/09/2026, 09:35</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>53,3%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 27.305.715,35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3,80%|Prefixada</x:t>
+    <x:t>59,7%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 27.328.540,75</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,20%|Prefixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -109,10 +109,10 @@
     <x:t>R$ 300.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 381.030,03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 368.875,53</x:t>
+    <x:t>R$ 381.381,26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 369.174,07</x:t>
   </x:si>
   <x:si>
     <x:t>CDB NBC BANK - AGO/2028</x:t>
@@ -130,10 +130,10 @@
     <x:t>R$ 200.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 257.526,02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 248.897,12</x:t>
+    <x:t>R$ 257.777,02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 249.110,47</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BANCO ANDBANK (BRASIL) S/ - AGO/2027</x:t>
@@ -148,10 +148,10 @@
     <x:t>R$ 250.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 315.722,62</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 305.864,23</x:t>
+    <x:t>R$ 316.006,72</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 306.105,71</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BANCO BBC - GRUPO SIMPAR - FEV/2027</x:t>
@@ -163,10 +163,10 @@
     <x:t>+12,30%</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 317.466,80</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 307.346,78</x:t>
+    <x:t>R$ 317.759,22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 307.595,34</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BANCO XP S.A. - AGO/2027</x:t>
@@ -175,10 +175,10 @@
     <x:t>+12,10%</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 316.303,46</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 306.357,94</x:t>
+    <x:t>R$ 316.590,33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 306.601,78</x:t>
   </x:si>
   <x:si>
     <x:t>CDB FACTA FINANCEIRA - FEV/2027</x:t>
@@ -190,13 +190,13 @@
     <x:t>+12,85%</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 256.418,81</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 247.955,99</x:t>
-  </x:si>
-  <x:si>
-    <x:t>47,60%|Pós-Fixada</x:t>
+    <x:t>R$ 256.664,94</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 248.165,20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>53,20%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>CDB ORIGINAL - AGO/2027</x:t>
@@ -208,10 +208,10 @@
     <x:t>117,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 272.890,14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 261.956,62</x:t>
+    <x:t>R$ 273.214,55</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 262.232,37</x:t>
   </x:si>
   <x:si>
     <x:t>LCA BNDES - MAI/2027</x:t>
@@ -235,7 +235,7 @@
     <x:t>R$ 20.228.598,57</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 21.032.512,29</x:t>
+    <x:t>R$ 21.050.568,73</x:t>
   </x:si>
   <x:si>
     <x:t>LCA BNDES - JUN/2028</x:t>
@@ -259,7 +259,7 @@
     <x:t>R$ 924.308,74</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 944.361,80</x:t>
+    <x:t>R$ 945.138,95</x:t>
   </x:si>
   <x:si>
     <x:t>LCA BNDES - AGO/2028</x:t>
@@ -277,7 +277,7 @@
     <x:t>R$ 988.914,13</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.010.368,81</x:t>
+    <x:t>R$ 1.011.200,28</x:t>
   </x:si>
   <x:si>
     <x:t>99,00</x:t>
@@ -286,10 +286,10 @@
     <x:t>R$ 1.100.028,08</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.123.893,40</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1,80%|Inflação</x:t>
+    <x:t>R$ 1.124.818,29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,00%|Inflação</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BTG PACTUAL - AGO/2027</x:t>
@@ -304,10 +304,10 @@
     <x:t>R$ 350.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 435.416,36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 422.603,91</x:t>
+    <x:t>R$ 435.495,58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 422.671,24</x:t>
   </x:si>
   <x:si>
     <x:t>LF BMG - AGO/2027</x:t>
@@ -319,10 +319,10 @@
     <x:t>7,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 445.426,59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 431.112,60</x:t>
+    <x:t>R$ 445.546,66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 431.214,66</x:t>
   </x:si>
   <x:si>
     <x:t>CDB BANCO PLENO - AGO/2028</x:t>
@@ -343,13 +343,13 @@
     <x:t>R$ 74.699,90</x:t>
   </x:si>
   <x:si>
-    <x:t>45,8%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 23.431.003,70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>45,70%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>39,3%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 18.008.941,80</x:t>
+  </x:si>
+  <x:si>
+    <x:t>39,30%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -364,187 +364,142 @@
     <x:t>Em cotização</x:t>
   </x:si>
   <x:si>
-    <x:t>BNP Paribas Match FIF RF CP RL</x:t>
+    <x:t>Solis Capital Antares Advisory FIC de FIDC</x:t>
   </x:si>
   <x:si>
     <x:t>21/09/2026</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 567,67</x:t>
-  </x:si>
-  <x:si>
-    <x:t>904,71</x:t>
+    <x:t>R$ 2,22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>282.831,90</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 513.571,60</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 510.517,99</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 274,82</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.460,17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.874.648,57</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.857.852,65</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Solis Capital Antares Advisory FIC de FIDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2,22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>282.831,90</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 626.751,68</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 611.585,61</x:t>
+    <x:t>R$ 627.476,49</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 612.201,70</x:t>
   </x:si>
   <x:si>
     <x:t>Riza Daikon Advisory FIF em Cotas de FIM</x:t>
   </x:si>
   <x:si>
-    <x:t>18/09/2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>R$ 1,93</x:t>
   </x:si>
   <x:si>
     <x:t>100.756,91</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 194.058,12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 192.886,05</x:t>
+    <x:t>R$ 194.281,65</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 193.076,05</x:t>
   </x:si>
   <x:si>
     <x:t>Valora Horizon High Yield FIDC</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 4.849.872,04</x:t>
+    <x:t>R$ 4.852.939,90</x:t>
   </x:si>
   <x:si>
     <x:t>0,98</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 4.759.615,38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 4.608.648,62</x:t>
+    <x:t>R$ 4.762.626,15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 4.611.207,78</x:t>
   </x:si>
   <x:si>
     <x:t>Brave 90 FIC FIDC</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2,19</x:t>
+    <x:t>R$ 2,20</x:t>
   </x:si>
   <x:si>
     <x:t>126.501,25</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 277.597,77</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 267.582,30</x:t>
+    <x:t>R$ 277.752,17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 267.713,54</x:t>
   </x:si>
   <x:si>
     <x:t>Jive BossaNova High Yield Advisory FIC FIDC</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 200,66</x:t>
+    <x:t>R$ 201,02</x:t>
   </x:si>
   <x:si>
     <x:t>30.298,33</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 6.079.587,35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.768.537,95</x:t>
+    <x:t>R$ 6.090.603,59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.777.901,76</x:t>
   </x:si>
   <x:si>
     <x:t>JGP Crédito Ecossistema 360 Advisory FIC de FIF Multimercado CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 184,66</x:t>
+    <x:t>R$ 184,87</x:t>
   </x:si>
   <x:si>
     <x:t>31.351,36</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 5.789.274,31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.767.311,86</x:t>
+    <x:t>R$ 5.795.790,25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.772.850,41</x:t>
   </x:si>
   <x:si>
     <x:t>Trend Cash CIC de Classes RF Simples RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 159,97</x:t>
+    <x:t>23/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 160,12</x:t>
   </x:si>
   <x:si>
     <x:t>507,28</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 81.147,31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 80.341,28</x:t>
+    <x:t>R$ 81.227,35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 80.403,31</x:t>
   </x:si>
   <x:si>
     <x:t>M8 Credit Opportunities FIC de FI em FIDC</x:t>
   </x:si>
   <x:si>
+    <x:t>22/09/2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>R$ 2,75</x:t>
   </x:si>
   <x:si>
     <x:t>65.114,40</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 178.971,77</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 172.496,18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1,49</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.383.301,60</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.055.779,84</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.043.229,38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,91%|Fundos Imobiliários</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 465.760,00</x:t>
+    <x:t>R$ 179.184,15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 172.676,70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,02%|Fundos Imobiliários</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 466.044,00</x:t>
   </x:si>
   <x:si>
     <x:t>Ativo</x:t>
@@ -583,16 +538,13 @@
     <x:t>R$ 102,50</x:t>
   </x:si>
   <x:si>
-    <x:t>-R$ 20,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 82,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,01%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.873,72</x:t>
+    <x:t>-R$ 19,95</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 82,05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.607,08</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -622,7 +574,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>5873,72</x:t>
+    <x:t>1607,08</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -1170,7 +1122,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K51"/>
+  <x:dimension ref="A1:K48"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="51.853482" style="0" customWidth="1"/>
@@ -1230,13 +1182,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>51208352.7681288</x:v>
+        <x:v>45805133.6261119</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>51202479.0481289</x:v>
+        <x:v>45803526.5461119</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>5873.72</x:v>
+        <x:v>1607.08</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -2028,22 +1980,22 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="B33" s="12" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="C33" s="12" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="C33" s="12" t="s">
+      <x:c r="D33" s="12" t="s">
         <x:v>130</x:v>
-      </x:c>
-      <x:c r="D33" s="12" t="s">
-        <x:v>131</x:v>
       </x:c>
       <x:c r="E33" s="12" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="F33" s="12" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="G33" s="12" t="s">
         <x:v>132</x:v>
-      </x:c>
-      <x:c r="G33" s="12" t="s">
-        <x:v>133</x:v>
       </x:c>
       <x:c r="H33" s="3"/>
       <x:c r="I33" s="3"/>
@@ -2052,25 +2004,25 @@
     </x:row>
     <x:row r="34" spans="1:11" ht="30" customHeight="1">
       <x:c r="A34" s="12" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B34" s="12" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="C34" s="12" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="B34" s="12" t="s">
+      <x:c r="D34" s="12" t="s">
         <x:v>135</x:v>
-      </x:c>
-      <x:c r="C34" s="12" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="D34" s="12" t="s">
-        <x:v>137</x:v>
       </x:c>
       <x:c r="E34" s="12" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="F34" s="12" t="s">
-        <x:v>138</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="G34" s="12" t="s">
-        <x:v>139</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="H34" s="3"/>
       <x:c r="I34" s="3"/>
@@ -2079,25 +2031,25 @@
     </x:row>
     <x:row r="35" spans="1:11" ht="30" customHeight="1">
       <x:c r="A35" s="12" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="B35" s="12" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="C35" s="12" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="D35" s="12" t="s">
         <x:v>140</x:v>
-      </x:c>
-      <x:c r="B35" s="12" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="C35" s="12" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="D35" s="12" t="s">
-        <x:v>142</x:v>
       </x:c>
       <x:c r="E35" s="12" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="F35" s="12" t="s">
-        <x:v>143</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="G35" s="12" t="s">
-        <x:v>144</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="H35" s="3"/>
       <x:c r="I35" s="3"/>
@@ -2106,25 +2058,25 @@
     </x:row>
     <x:row r="36" spans="1:11" ht="30" customHeight="1">
       <x:c r="A36" s="12" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="B36" s="12" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="C36" s="12" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="D36" s="12" t="s">
         <x:v>145</x:v>
-      </x:c>
-      <x:c r="B36" s="12" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="C36" s="12" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="D36" s="12" t="s">
-        <x:v>147</x:v>
       </x:c>
       <x:c r="E36" s="12" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="F36" s="12" t="s">
-        <x:v>148</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="G36" s="12" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="H36" s="3"/>
       <x:c r="I36" s="3"/>
@@ -2133,25 +2085,25 @@
     </x:row>
     <x:row r="37" spans="1:11" ht="30" customHeight="1">
       <x:c r="A37" s="12" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="B37" s="12" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="C37" s="12" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="B37" s="12" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="C37" s="12" t="s">
+      <x:c r="D37" s="12" t="s">
         <x:v>151</x:v>
-      </x:c>
-      <x:c r="D37" s="12" t="s">
-        <x:v>152</x:v>
       </x:c>
       <x:c r="E37" s="12" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="F37" s="12" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="G37" s="12" t="s">
         <x:v>153</x:v>
-      </x:c>
-      <x:c r="G37" s="12" t="s">
-        <x:v>154</x:v>
       </x:c>
       <x:c r="H37" s="3"/>
       <x:c r="I37" s="3"/>
@@ -2159,25 +2111,25 @@
       <x:c r="K37" s="3"/>
     </x:row>
     <x:row r="38" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A38" s="12" t="s">
+      <x:c r="A38" s="13" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="B38" s="13" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="B38" s="12" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="C38" s="12" t="s">
+      <x:c r="C38" s="13" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="D38" s="12" t="s">
+      <x:c r="D38" s="13" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="E38" s="12" t="s">
+      <x:c r="E38" s="13" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="F38" s="12" t="s">
+      <x:c r="F38" s="13" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="G38" s="12" t="s">
+      <x:c r="G38" s="13" t="s">
         <x:v>159</x:v>
       </x:c>
       <x:c r="H38" s="3"/>
@@ -2185,115 +2137,117 @@
       <x:c r="J38" s="3"/>
       <x:c r="K38" s="3"/>
     </x:row>
-    <x:row r="39" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A39" s="12" t="s">
+    <x:row r="39" spans="1:11">
+      <x:c r="A39" s="4"/>
+      <x:c r="B39" s="4"/>
+      <x:c r="C39" s="4"/>
+      <x:c r="D39" s="4"/>
+      <x:c r="E39" s="4"/>
+      <x:c r="F39" s="4"/>
+      <x:c r="G39" s="4"/>
+      <x:c r="H39" s="4"/>
+      <x:c r="I39" s="4"/>
+      <x:c r="J39" s="4"/>
+      <x:c r="K39" s="4"/>
+    </x:row>
+    <x:row r="40" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A40" s="8" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="B39" s="12" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="C39" s="12" t="s">
+      <x:c r="B40" s="9"/>
+      <x:c r="C40" s="9"/>
+      <x:c r="D40" s="9"/>
+      <x:c r="E40" s="9"/>
+      <x:c r="F40" s="9"/>
+      <x:c r="G40" s="9"/>
+      <x:c r="H40" s="9"/>
+      <x:c r="I40" s="9"/>
+      <x:c r="J40" s="9"/>
+      <x:c r="K40" s="10" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="D39" s="12" t="s">
+    </x:row>
+    <x:row r="41" spans="1:11">
+      <x:c r="A41" s="4"/>
+      <x:c r="B41" s="4"/>
+      <x:c r="C41" s="4"/>
+      <x:c r="D41" s="4"/>
+      <x:c r="E41" s="4"/>
+      <x:c r="F41" s="4"/>
+      <x:c r="G41" s="4"/>
+      <x:c r="H41" s="4"/>
+      <x:c r="I41" s="4"/>
+      <x:c r="J41" s="4"/>
+      <x:c r="K41" s="4"/>
+    </x:row>
+    <x:row r="42" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A42" s="11" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="E39" s="12" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="F39" s="12" t="s">
+      <x:c r="B42" s="11" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="G39" s="12" t="s">
+      <x:c r="C42" s="11" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="H39" s="3"/>
-      <x:c r="I39" s="3"/>
-      <x:c r="J39" s="3"/>
-      <x:c r="K39" s="3"/>
-    </x:row>
-    <x:row r="40" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A40" s="12" t="s">
+      <x:c r="D42" s="11" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="B40" s="12" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="C40" s="12" t="s">
+      <x:c r="E42" s="11" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="D40" s="12" t="s">
+      <x:c r="F42" s="11" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="E40" s="12" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="F40" s="12" t="s">
+      <x:c r="G42" s="11" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="G40" s="12" t="s">
+      <x:c r="H42" s="11" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="I42" s="11" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="H40" s="3"/>
-      <x:c r="I40" s="3"/>
-      <x:c r="J40" s="3"/>
-      <x:c r="K40" s="3"/>
-    </x:row>
-    <x:row r="41" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A41" s="13" t="s">
+      <x:c r="J42" s="11" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="B41" s="13" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="C41" s="13" t="s">
+      <x:c r="K42" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A43" s="13" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="D41" s="13" t="s">
+      <x:c r="B43" s="13" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="E41" s="13" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="F41" s="13" t="s">
+      <x:c r="C43" s="13" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D43" s="13" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E43" s="13" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F43" s="13" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="G43" s="13" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="G41" s="13" t="s">
+      <x:c r="H43" s="13" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="I43" s="13" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="H41" s="3"/>
-      <x:c r="I41" s="3"/>
-      <x:c r="J41" s="3"/>
-      <x:c r="K41" s="3"/>
-    </x:row>
-    <x:row r="42" spans="1:11">
-      <x:c r="A42" s="4"/>
-      <x:c r="B42" s="4"/>
-      <x:c r="C42" s="4"/>
-      <x:c r="D42" s="4"/>
-      <x:c r="E42" s="4"/>
-      <x:c r="F42" s="4"/>
-      <x:c r="G42" s="4"/>
-      <x:c r="H42" s="4"/>
-      <x:c r="I42" s="4"/>
-      <x:c r="J42" s="4"/>
-      <x:c r="K42" s="4"/>
-    </x:row>
-    <x:row r="43" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A43" s="8" t="s">
+      <x:c r="J43" s="13" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="B43" s="9"/>
-      <x:c r="C43" s="9"/>
-      <x:c r="D43" s="9"/>
-      <x:c r="E43" s="9"/>
-      <x:c r="F43" s="9"/>
-      <x:c r="G43" s="9"/>
-      <x:c r="H43" s="9"/>
-      <x:c r="I43" s="9"/>
-      <x:c r="J43" s="9"/>
-      <x:c r="K43" s="10" t="s">
-        <x:v>176</x:v>
+      <x:c r="K43" s="13" t="s">
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
@@ -2309,187 +2263,104 @@
       <x:c r="J44" s="4"/>
       <x:c r="K44" s="4"/>
     </x:row>
-    <x:row r="45" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A45" s="11" t="s">
+    <x:row r="45" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A45" s="8" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B45" s="9"/>
+      <x:c r="C45" s="9"/>
+      <x:c r="D45" s="9"/>
+      <x:c r="E45" s="9"/>
+      <x:c r="F45" s="9"/>
+      <x:c r="G45" s="9"/>
+      <x:c r="H45" s="9"/>
+      <x:c r="I45" s="9"/>
+      <x:c r="J45" s="9"/>
+      <x:c r="K45" s="10" t="s">
+        <x:v>176</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:11">
+      <x:c r="A46" s="4"/>
+      <x:c r="B46" s="4"/>
+      <x:c r="C46" s="4"/>
+      <x:c r="D46" s="4"/>
+      <x:c r="E46" s="4"/>
+      <x:c r="F46" s="4"/>
+      <x:c r="G46" s="4"/>
+      <x:c r="H46" s="4"/>
+      <x:c r="I46" s="4"/>
+      <x:c r="J46" s="4"/>
+      <x:c r="K46" s="4"/>
+    </x:row>
+    <x:row r="47" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A47" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B47" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C47" s="11" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="B45" s="11" t="s">
+      <x:c r="D47" s="11" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="C45" s="11" t="s">
+      <x:c r="E47" s="11" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="D45" s="11" t="s">
+      <x:c r="F47" s="11" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="E45" s="11" t="s">
+      <x:c r="G47" s="11" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="F45" s="11" t="s">
+      <x:c r="H47" s="11" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="G45" s="11" t="s">
+      <x:c r="I47" s="11" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="H45" s="11" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="I45" s="11" t="s">
+      <x:c r="J47" s="11" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="J45" s="11" t="s">
+      <x:c r="K47" s="11" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="K45" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A46" s="13" t="s">
+    </x:row>
+    <x:row r="48" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A48" s="13" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="B46" s="13" t="s">
+      <x:c r="B48" s="13" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="C46" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D46" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E46" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F46" s="13" t="s">
+      <x:c r="C48" s="13" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="G46" s="13" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="H46" s="13" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="I46" s="13" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="J46" s="13" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="K46" s="13" t="s">
-        <x:v>176</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:11">
-      <x:c r="A47" s="4"/>
-      <x:c r="B47" s="4"/>
-      <x:c r="C47" s="4"/>
-      <x:c r="D47" s="4"/>
-      <x:c r="E47" s="4"/>
-      <x:c r="F47" s="4"/>
-      <x:c r="G47" s="4"/>
-      <x:c r="H47" s="4"/>
-      <x:c r="I47" s="4"/>
-      <x:c r="J47" s="4"/>
-      <x:c r="K47" s="4"/>
-    </x:row>
-    <x:row r="48" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A48" s="8" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="B48" s="9"/>
-      <x:c r="C48" s="9"/>
-      <x:c r="D48" s="9"/>
-      <x:c r="E48" s="9"/>
-      <x:c r="F48" s="9"/>
-      <x:c r="G48" s="9"/>
-      <x:c r="H48" s="9"/>
-      <x:c r="I48" s="9"/>
-      <x:c r="J48" s="9"/>
-      <x:c r="K48" s="10" t="s">
-        <x:v>192</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:11">
-      <x:c r="A49" s="4"/>
-      <x:c r="B49" s="4"/>
-      <x:c r="C49" s="4"/>
-      <x:c r="D49" s="4"/>
-      <x:c r="E49" s="4"/>
-      <x:c r="F49" s="4"/>
-      <x:c r="G49" s="4"/>
-      <x:c r="H49" s="4"/>
-      <x:c r="I49" s="4"/>
-      <x:c r="J49" s="4"/>
-      <x:c r="K49" s="4"/>
-    </x:row>
-    <x:row r="50" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A50" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B50" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C50" s="11" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="D50" s="11" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="E50" s="11" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="F50" s="11" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="G50" s="11" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="H50" s="11" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="I50" s="11" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="J50" s="11" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="K50" s="11" t="s">
-        <x:v>201</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A51" s="13" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="B51" s="13" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="C51" s="13" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D51" s="13" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="E51" s="13" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="F51" s="13" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="G51" s="13" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="H51" s="13" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="I51" s="13" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="J51" s="13" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="K51" s="13" t="s">
-        <x:v>203</x:v>
+      <x:c r="D48" s="13" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="E48" s="13" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="F48" s="13" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="G48" s="13" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="H48" s="13" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="I48" s="13" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="J48" s="13" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="K48" s="13" t="s">
+        <x:v>187</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2498,8 +2369,8 @@
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
     <x:mergeCell ref="A28:F28"/>
-    <x:mergeCell ref="A43:J43"/>
-    <x:mergeCell ref="A48:J48"/>
+    <x:mergeCell ref="A40:J40"/>
+    <x:mergeCell ref="A45:J45"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
